--- a/excel-templates/経営管理_テンプレート.xlsx
+++ b/excel-templates/経営管理_テンプレート.xlsx
@@ -10435,7 +10435,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="C2:C201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"梶原通信,秀電工,井本貴史,LLS電気株式会社,トラストテクノス株式会社,株式会社RISE"</formula1>
+      <formula1>"梶原通信,秀電工,井本貴史,LLS電気,株式会社トラストテクノス,株式会社RISE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16067,12 +16067,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LLS電気株式会社</t>
+          <t>LLS電気</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>法人</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16089,7 +16089,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>トラストテクノス株式会社</t>
+          <t>株式会社トラストテクノス</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">

--- a/excel-templates/経営管理_テンプレート.xlsx
+++ b/excel-templates/経営管理_テンプレート.xlsx
@@ -16674,7 +16674,11 @@
       <c r="F3" s="20" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n"/>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>源地健史</t>
+        </is>
+      </c>
       <c r="B4" s="17" t="n"/>
       <c r="C4" s="17" t="n"/>
       <c r="D4" s="17">
@@ -16760,6 +16764,17 @@
       </c>
       <c r="E11" s="19" t="n"/>
       <c r="F11" s="20" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17">
+        <f>IF(B12="","",B12-C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">

--- a/excel-templates/経営管理_テンプレート.xlsx
+++ b/excel-templates/経営管理_テンプレート.xlsx
@@ -16646,7 +16646,7 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>野添優</t>
+          <t>丸田翔吾</t>
         </is>
       </c>
       <c r="B2" s="17" t="n"/>
@@ -16661,7 +16661,7 @@
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>丸田翔吾</t>
+          <t>源地健史</t>
         </is>
       </c>
       <c r="B3" s="21" t="n"/>
@@ -16674,11 +16674,7 @@
       <c r="F3" s="20" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>源地健史</t>
-        </is>
-      </c>
+      <c r="A4" s="16" t="n"/>
       <c r="B4" s="17" t="n"/>
       <c r="C4" s="17" t="n"/>
       <c r="D4" s="17">
@@ -16764,17 +16760,6 @@
       </c>
       <c r="E11" s="19" t="n"/>
       <c r="F11" s="20" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17">
-        <f>IF(B12="","",B12-C12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">

--- a/excel-templates/経営管理_テンプレート.xlsx
+++ b/excel-templates/経営管理_テンプレート.xlsx
@@ -16791,7 +16791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16815,7 +16815,17 @@
           <t>得意先名</t>
         </is>
       </c>
+      <c r="F1" s="22" t="inlineStr">
+        <is>
+          <t>締日</t>
+        </is>
+      </c>
       <c r="G1" s="22" t="inlineStr">
+        <is>
+          <t>入金サイト</t>
+        </is>
+      </c>
+      <c r="I1" s="22" t="inlineStr">
         <is>
           <t>経費種類</t>
         </is>
@@ -16842,7 +16852,17 @@
           <t>港振興業株式会社</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>月末</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>翌月末</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>材料費</t>
         </is>
@@ -16869,7 +16889,17 @@
           <t>株式会社トラストテクノス</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>月末</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>翌月末</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>燃料費</t>
         </is>
@@ -16896,7 +16926,17 @@
           <t>有限会社平成システム</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20日</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t>翌月末</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>高速料金</t>
         </is>
@@ -16923,7 +16963,17 @@
           <t>FGE合同会社</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>月末</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>翌月末</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>駐車場代</t>
         </is>
@@ -16950,7 +17000,17 @@
           <t>mtr株式会社</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>月末</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
+        <is>
+          <t>翌月末</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>工具・消耗品費</t>
         </is>
@@ -16977,7 +17037,17 @@
           <t>株式会社オークコミュニケーション</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>月末</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>翌々月10日</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>通信費</t>
         </is>
@@ -16989,7 +17059,17 @@
           <t>株式会社ライズ</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>確認中</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
+        <is>
+          <t>確認中</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>交際費</t>
         </is>
@@ -17001,7 +17081,17 @@
           <t>千里スカイハイツ管理組合</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>月末</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
+        <is>
+          <t>翌々月末</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>会議費</t>
         </is>
@@ -17013,7 +17103,17 @@
           <t>菊次</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>月末</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>翌月末</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>事務用品費</t>
         </is>
@@ -17025,49 +17125,59 @@
           <t>ページ</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>都度</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t>都度</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>広告宣伝費</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>研修費</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>福利厚生費</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>車両維持費</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>地代家賃</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>保険料</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>雑費</t>
         </is>
